--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDBA6975-99E3-4E17-890E-869CF76CF8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAC1941F-EB1B-40F0-A9F4-F3EBA4CF72CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22739055-B31E-46A6-80A4-982AFE2867A5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5F700A36-EFF5-4D00-8B5E-C09424C97A69}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D282E24C-1402-4370-9637-2C1C4A842547}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C9109E-4FA7-48E5-91EF-60338E619C88}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAC1941F-EB1B-40F0-A9F4-F3EBA4CF72CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B098741-8F38-44FC-9464-6E0E55DF717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5F700A36-EFF5-4D00-8B5E-C09424C97A69}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DD0B277E-1567-456B-A253-B1812FFB13D5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C9109E-4FA7-48E5-91EF-60338E619C88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F332F3B-55AD-476E-BC25-FEAB697F4EF7}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B098741-8F38-44FC-9464-6E0E55DF717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{623BDD38-D562-498B-9A5A-78B4DB66ECC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DD0B277E-1567-456B-A253-B1812FFB13D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{55251BBD-15E1-4347-B024-342EDE120095}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F332F3B-55AD-476E-BC25-FEAB697F4EF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B803CD-60CF-4472-A1C2-BBBA9E006A84}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{623BDD38-D562-498B-9A5A-78B4DB66ECC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{099CEE79-25BE-404E-90A9-1C1513BCF2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{55251BBD-15E1-4347-B024-342EDE120095}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{65628C45-0D2F-4722-AF6A-F67839AF8BFA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B803CD-60CF-4472-A1C2-BBBA9E006A84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D35936-4D6D-4912-9194-D054992DCD67}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{099CEE79-25BE-404E-90A9-1C1513BCF2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7797B566-3EE7-429A-8AEF-4E33D7290B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{65628C45-0D2F-4722-AF6A-F67839AF8BFA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3F9E390A-A21A-4777-B73B-3FA270E568DD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D35936-4D6D-4912-9194-D054992DCD67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3390B3C1-285B-47E3-8EC8-F9CCFF4E510D}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7797B566-3EE7-429A-8AEF-4E33D7290B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7E48158-6726-4B81-B2C3-1DD52BAC509A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3F9E390A-A21A-4777-B73B-3FA270E568DD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A897DA3B-EE1A-497D-8CCD-4C4480C494E2}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3390B3C1-285B-47E3-8EC8-F9CCFF4E510D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E06D6D-E773-4BCC-98E8-6FE3B209251F}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7E48158-6726-4B81-B2C3-1DD52BAC509A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92F32260-CC5F-47FD-B759-07F22D36C061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A897DA3B-EE1A-497D-8CCD-4C4480C494E2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{95830734-9865-43DB-8A95-A952B8FB04A0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E06D6D-E773-4BCC-98E8-6FE3B209251F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABF41605-0FEA-4363-99E0-822A32D9A524}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92F32260-CC5F-47FD-B759-07F22D36C061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61EF723E-C215-47EE-9798-F88B33321BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{95830734-9865-43DB-8A95-A952B8FB04A0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CD246060-D3F5-49C3-8CFE-6454A40F39DD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABF41605-0FEA-4363-99E0-822A32D9A524}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A069006-F24D-47F0-94D4-137A6BF89BBB}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61EF723E-C215-47EE-9798-F88B33321BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5EFA2C7-348D-4468-8518-486E99EA7E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CD246060-D3F5-49C3-8CFE-6454A40F39DD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{36DBA7B3-0D29-4E67-8522-3598DCD14131}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A069006-F24D-47F0-94D4-137A6BF89BBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0B481C-F291-4707-B137-75630417E530}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5EFA2C7-348D-4468-8518-486E99EA7E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D93C3A6C-98F4-4F11-81A9-E925B692ABF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{36DBA7B3-0D29-4E67-8522-3598DCD14131}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{89D51455-757C-4337-8D13-A23FE9C655F1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0B481C-F291-4707-B137-75630417E530}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1D636E-553A-4101-853E-9B881B1E5A43}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D93C3A6C-98F4-4F11-81A9-E925B692ABF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57170BCE-1330-409E-9DB9-877B94A44D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{89D51455-757C-4337-8D13-A23FE9C655F1}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{2EE7CBB6-608D-4B34-987E-49E4EC985A1F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1D636E-553A-4101-853E-9B881B1E5A43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C3CE3E-B20B-42E7-8D18-B80A0257587C}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57170BCE-1330-409E-9DB9-877B94A44D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F2F1EBE-93D5-41DF-92E1-2DAC77A70D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{2EE7CBB6-608D-4B34-987E-49E4EC985A1F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FF924F9B-D280-4AE3-9779-29B632C97B6B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C3CE3E-B20B-42E7-8D18-B80A0257587C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B16F2FA-90B0-4037-B8D6-0E454855CEEE}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F2F1EBE-93D5-41DF-92E1-2DAC77A70D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ACD2ADF-E07A-46CD-B9F9-3A123DA4D04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FF924F9B-D280-4AE3-9779-29B632C97B6B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E69ED1F9-A4B7-47C2-AA60-5D5EB84A3D0A}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B16F2FA-90B0-4037-B8D6-0E454855CEEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE91CFC2-BBB0-410A-9B74-C81433549035}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ACD2ADF-E07A-46CD-B9F9-3A123DA4D04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0FDCEB1-E364-45F2-950F-BF42B91DD6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E69ED1F9-A4B7-47C2-AA60-5D5EB84A3D0A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E3CE05C3-948E-4E1C-A2C0-8B7A2542FEB4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE91CFC2-BBB0-410A-9B74-C81433549035}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77559B56-5E49-4E80-82FB-BB6A81CEF2B4}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0FDCEB1-E364-45F2-950F-BF42B91DD6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F20FB53D-1B89-474E-AB25-D54143FFDB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E3CE05C3-948E-4E1C-A2C0-8B7A2542FEB4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D05F7CF8-528F-42EE-BB1E-F615D25467BC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77559B56-5E49-4E80-82FB-BB6A81CEF2B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1BD14A1-57A0-48B6-AA81-AD9933091DCB}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F20FB53D-1B89-474E-AB25-D54143FFDB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C93D5430-9052-4AAB-93FB-ED47B6522194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D05F7CF8-528F-42EE-BB1E-F615D25467BC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{71B95A06-CD34-41B0-AB32-A2D280E997B2}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1BD14A1-57A0-48B6-AA81-AD9933091DCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE8E303-76F1-4C04-A16F-43273BAA2240}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB5894C1-2943-4B3D-9689-CBAD2408575B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9365ECF-1661-496E-A5D8-C682FB8858AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{620623D5-81E2-40EA-A6EE-687DF77A4ED4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9C50738E-D02F-4B35-A7DE-7ECDF67B0AB0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63352416-E9EF-4C28-A1E1-5F6B98CA58AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91961B69-0EC1-4AED-A740-1F48EAE76B5E}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9365ECF-1661-496E-A5D8-C682FB8858AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0640BDA4-9E3F-4EB9-A658-D6A77509FEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9C50738E-D02F-4B35-A7DE-7ECDF67B0AB0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B7826876-F369-4AD0-8D3A-E3AB2885CAE0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91961B69-0EC1-4AED-A740-1F48EAE76B5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF389771-A1A6-466C-B3B1-C47FFB3B66A1}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0640BDA4-9E3F-4EB9-A658-D6A77509FEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D820B866-C6F2-46FF-A4E1-53E19AC6C77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B7826876-F369-4AD0-8D3A-E3AB2885CAE0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{43AA0CE1-06C9-454F-A03E-7B6D96ED585C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF389771-A1A6-466C-B3B1-C47FFB3B66A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7FE0E1-A564-4BD2-B2C4-10C287F5A3F1}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D820B866-C6F2-46FF-A4E1-53E19AC6C77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52312E4B-F398-4233-871A-F04D471C610B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{43AA0CE1-06C9-454F-A03E-7B6D96ED585C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{36196C07-ED76-4465-8DD7-CEC8D94D1E5A}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7FE0E1-A564-4BD2-B2C4-10C287F5A3F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A18E50-3FB7-497A-AFB8-41E6E18AC1EF}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52312E4B-F398-4233-871A-F04D471C610B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EB8F42E-B4EF-4825-B2BB-65BDC68A85AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{36196C07-ED76-4465-8DD7-CEC8D94D1E5A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{93881A43-68E5-4B42-B316-2F118F960D7C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A18E50-3FB7-497A-AFB8-41E6E18AC1EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579DBDFA-8C13-47CD-9626-33DA3E888617}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EB8F42E-B4EF-4825-B2BB-65BDC68A85AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D85D91DF-2F62-41C7-91A2-3621575C9574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{93881A43-68E5-4B42-B316-2F118F960D7C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3C836BB-97C3-4B75-BFA2-F311CD2360B3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579DBDFA-8C13-47CD-9626-33DA3E888617}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D98270-FF16-4344-B433-FEB493EFB584}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D85D91DF-2F62-41C7-91A2-3621575C9574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5BC61AE-B376-4C80-9C25-CCFD3B54E28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3C836BB-97C3-4B75-BFA2-F311CD2360B3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9D6C3CD5-4E3B-4A52-A544-5F8D3FD9A4E0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D98270-FF16-4344-B433-FEB493EFB584}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9A2FF1-3283-45DE-9248-F660BAA8BE9A}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5BC61AE-B376-4C80-9C25-CCFD3B54E28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEA27016-9656-45D1-A9A8-377AE69D103F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9D6C3CD5-4E3B-4A52-A544-5F8D3FD9A4E0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3F4BD656-BE6B-4A83-BC69-9C9F5911D67C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9A2FF1-3283-45DE-9248-F660BAA8BE9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03271433-9133-404E-8192-34DD46EA0ADC}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEA27016-9656-45D1-A9A8-377AE69D103F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86CDCBF4-189A-49DB-9D27-4D34F6D5BECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3F4BD656-BE6B-4A83-BC69-9C9F5911D67C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BAD9CE3D-90B3-4D5E-9300-D4B23DACBE68}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03271433-9133-404E-8192-34DD46EA0ADC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFE11E7-BED9-4A41-84FF-419B4AAAC8EA}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86CDCBF4-189A-49DB-9D27-4D34F6D5BECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D645BF0-5686-4F65-9240-EE9EC80F552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BAD9CE3D-90B3-4D5E-9300-D4B23DACBE68}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3286EF9-746B-430D-8AED-C69826C868AE}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFE11E7-BED9-4A41-84FF-419B4AAAC8EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BB5DA8-A8D9-4301-93FC-2D8F4D8699E8}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D645BF0-5686-4F65-9240-EE9EC80F552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADCE91EB-FE55-467A-8D44-9F8DA14F199D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3286EF9-746B-430D-8AED-C69826C868AE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CD1D3CAD-C69F-41E7-B8AC-E4A2B6D540AD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BB5DA8-A8D9-4301-93FC-2D8F4D8699E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE444432-1421-4D13-AC1E-64264252DECA}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADCE91EB-FE55-467A-8D44-9F8DA14F199D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF514222-B5A0-47F7-9A0B-173CE9880FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CD1D3CAD-C69F-41E7-B8AC-E4A2B6D540AD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7A019580-4D86-41A1-82FE-EE1F4187C44F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE444432-1421-4D13-AC1E-64264252DECA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{449DABD5-D7AD-4F88-9BF2-653E506AB324}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF514222-B5A0-47F7-9A0B-173CE9880FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5F5EBFA-1826-40CC-9237-496F9A695CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7A019580-4D86-41A1-82FE-EE1F4187C44F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{490C4BA7-3B0E-417F-A5BE-E5E3E0FF5443}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{449DABD5-D7AD-4F88-9BF2-653E506AB324}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ECB999-A707-4BA1-BAED-49FC058BC93F}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5F5EBFA-1826-40CC-9237-496F9A695CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F1909F4-0F10-4407-A87C-F6834482511D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{490C4BA7-3B0E-417F-A5BE-E5E3E0FF5443}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{463C45D9-998D-46BD-9CD6-750D433AABC3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ECB999-A707-4BA1-BAED-49FC058BC93F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB6449D-C8D1-4F31-BD5A-EF7496CD33EB}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F1909F4-0F10-4407-A87C-F6834482511D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E029D3FE-C8EB-4506-83FC-4AD99022A9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{463C45D9-998D-46BD-9CD6-750D433AABC3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{169E4BF0-FA42-4C7E-AA0F-B88B2BB4ED5C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB6449D-C8D1-4F31-BD5A-EF7496CD33EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF42833-0A77-4768-AD0B-1907D2D35470}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E029D3FE-C8EB-4506-83FC-4AD99022A9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C89C81D-B475-4F1F-A5AA-39107DF68B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{169E4BF0-FA42-4C7E-AA0F-B88B2BB4ED5C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AD30F863-36CD-4686-B398-BF1F504EEBD1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF42833-0A77-4768-AD0B-1907D2D35470}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4523571E-7B9B-42C6-91DD-734DB54B9EA4}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C89C81D-B475-4F1F-A5AA-39107DF68B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AFB8A83-E65A-4DB3-A8BC-A2E7761EC178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AD30F863-36CD-4686-B398-BF1F504EEBD1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA3E670F-DF1C-49A1-8103-0FB4F2702B68}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4523571E-7B9B-42C6-91DD-734DB54B9EA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76D82D97-6D32-412B-B601-FED73DE8A12D}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AFB8A83-E65A-4DB3-A8BC-A2E7761EC178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E179510A-1D87-43A9-95B7-A6D27DCD9C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA3E670F-DF1C-49A1-8103-0FB4F2702B68}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2B8C9C5B-BDBF-4AA6-8746-36A8BDC032CB}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76D82D97-6D32-412B-B601-FED73DE8A12D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFD348F-4AF9-488A-BA4F-39E13FDBFC04}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E179510A-1D87-43A9-95B7-A6D27DCD9C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF3D132C-7D56-4D11-A5DF-D1A0260B78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2B8C9C5B-BDBF-4AA6-8746-36A8BDC032CB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CC23240B-CC4C-4B1A-AFE3-04A56EEB4E13}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFD348F-4AF9-488A-BA4F-39E13FDBFC04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741B968B-FB0D-4029-A577-F52461098D94}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF3D132C-7D56-4D11-A5DF-D1A0260B78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C56401C1-C2D8-4BD2-9862-EBEA9B7DB191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CC23240B-CC4C-4B1A-AFE3-04A56EEB4E13}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5E92F8D6-2357-45FA-BB25-2804DB909C5E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1963,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741B968B-FB0D-4029-A577-F52461098D94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{646628B5-BC63-4F98-B4E4-C5FAAAB18960}">
   <dimension ref="B3:L222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
